--- a/data/trans_dic/P1432-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1432-Edad-trans_dic.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,8</t>
+          <t>0,08; 0,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,78</t>
+          <t>0,07; 0,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,65</t>
+          <t>0,07; 0,58</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,37 +1018,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,86</t>
+          <t>0,19; 1,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,49</t>
+          <t>0,16; 1,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,48</t>
+          <t>0,16; 1,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,27</t>
+          <t>0,2; 1,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,93</t>
+          <t>0,16; 0,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,85</t>
+          <t>0,15; 0,86</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,55</t>
+          <t>0,43; 2,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,26</t>
+          <t>1,23; 4,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,16</t>
+          <t>1,16; 4,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,36</t>
+          <t>0,88; 3,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,83</t>
+          <t>0,98; 2,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,47</t>
+          <t>0,72; 2,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,0</t>
+          <t>0,49; 2,02</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,12</t>
+          <t>1,86; 6,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,57</t>
+          <t>1,74; 6,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,34</t>
+          <t>0,28; 2,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,89</t>
+          <t>1,7; 5,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,73</t>
+          <t>1,16; 5,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,45</t>
+          <t>1,05; 4,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,25</t>
+          <t>2,37; 5,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,27</t>
+          <t>1,92; 5,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,92</t>
+          <t>0,95; 2,85</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 11,75</t>
+          <t>4,37; 11,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,05</t>
+          <t>0,73; 4,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,76</t>
+          <t>2,64; 7,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,95; 9,56</t>
+          <t>4,1; 10,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 11,73</t>
+          <t>5,87; 11,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,27</t>
+          <t>4,36; 10,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,69; 9,4</t>
+          <t>4,93; 9,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,11; 7,95</t>
+          <t>4,25; 8,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,28; 8,19</t>
+          <t>4,25; 8,31</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,51</t>
+          <t>0,8; 1,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,01</t>
+          <t>0,42; 1,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,77</t>
+          <t>0,31; 0,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,01</t>
+          <t>1,11; 1,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,12</t>
+          <t>1,23; 2,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,96</t>
+          <t>0,99; 1,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,6</t>
+          <t>1,03; 1,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,45</t>
+          <t>0,89; 1,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,26</t>
+          <t>0,78; 1,28</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4581</t>
+          <t>0; 4618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4605</t>
+          <t>0; 4591</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5045</t>
+          <t>0; 5053</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6027</t>
+          <t>0; 6038</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 8611</t>
+          <t>0; 7305</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 8230</t>
+          <t>0; 7281</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 7407</t>
+          <t>0; 6973</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2091,32 +2091,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6737</t>
+          <t>0; 7112</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6514</t>
+          <t>0; 7587</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>877; 7823</t>
+          <t>883; 7834</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1041; 10676</t>
+          <t>1021; 9639</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1027; 10853</t>
+          <t>1003; 8872</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>878; 8649</t>
+          <t>882; 7720</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5534</t>
+          <t>0; 6433</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 7005</t>
+          <t>0; 7035</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5188</t>
+          <t>0; 4774</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>978; 9589</t>
+          <t>978; 9866</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>973; 9157</t>
+          <t>976; 9360</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1036; 9614</t>
+          <t>1044; 10345</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2732; 13168</t>
+          <t>2110; 12466</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2020; 11440</t>
+          <t>1946; 11206</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1951; 11051</t>
+          <t>1973; 11181</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1706; 9850</t>
+          <t>1668; 9488</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7323</t>
+          <t>0; 7312</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6758</t>
+          <t>0; 5192</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4200; 17216</t>
+          <t>4951; 17284</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5192; 18641</t>
+          <t>5186; 17953</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4330; 16683</t>
+          <t>4353; 16730</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7116; 22375</t>
+          <t>7753; 21774</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6249; 21708</t>
+          <t>6290; 20803</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5488; 19512</t>
+          <t>4736; 19689</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5537; 17917</t>
+          <t>5441; 18341</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5414; 23463</t>
+          <t>5393; 20770</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>943; 7818</t>
+          <t>943; 8687</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5905; 20200</t>
+          <t>5823; 19639</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4853; 20302</t>
+          <t>4098; 17889</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4055; 16819</t>
+          <t>3970; 15903</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14920; 33375</t>
+          <t>15034; 35125</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13180; 34965</t>
+          <t>12717; 34375</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6721; 20821</t>
+          <t>6767; 20298</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9533; 24651</t>
+          <t>9170; 24908</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1824; 10127</t>
+          <t>1818; 10955</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7123; 19938</t>
+          <t>6794; 20032</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13196; 31929</t>
+          <t>13697; 34885</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22436; 45494</t>
+          <t>22753; 46027</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17576; 41102</t>
+          <t>17440; 40891</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25497; 51132</t>
+          <t>26785; 51647</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>26208; 50715</t>
+          <t>27102; 51620</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28149; 53800</t>
+          <t>27952; 54607</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>26480; 49392</t>
+          <t>26081; 49788</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13565; 34740</t>
+          <t>14263; 35835</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10591; 26279</t>
+          <t>10477; 27785</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>38308; 68044</t>
+          <t>37609; 66395</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>43029; 75272</t>
+          <t>43559; 73835</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>38462; 69353</t>
+          <t>35140; 67268</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>68992; 106354</t>
+          <t>68472; 106966</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>64090; 101372</t>
+          <t>62191; 100231</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53794; 87626</t>
+          <t>54011; 88710</t>
         </is>
       </c>
     </row>
